--- a/elmclient/tests/tests_710.xlsx
+++ b/elmclient/tests/tests_710.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2853AD3-CB6E-4CE1-AAE6-9E744B5AFA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30AFF66-152B-44FD-B671-806EF962C1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2500" yWindow="110" windowWidth="28170" windowHeight="16500" xr2:uid="{E12FDD20-F1C7-4695-B929-60D3CA2A8B69}"/>
+    <workbookView xWindow="24975" yWindow="-20460" windowWidth="28800" windowHeight="15225" xr2:uid="{E12FDD20-F1C7-4695-B929-60D3CA2A8B69}"/>
   </bookViews>
   <sheets>
     <sheet name="rmqueries" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="241">
   <si>
     <t>oslc_rm:uses</t>
   </si>
@@ -727,6 +727,30 @@
   </si>
   <si>
     <t>dcterms:title,rdf:type,oslc:instanceShape</t>
+  </si>
+  <si>
+    <t># jazz.net check that auth works</t>
+  </si>
+  <si>
+    <t>@../../ianjazznet.creds</t>
+  </si>
+  <si>
+    <t>https://jazz.net</t>
+  </si>
+  <si>
+    <t>ccm:jazz03</t>
+  </si>
+  <si>
+    <t>Read jazz.net workitems</t>
+  </si>
+  <si>
+    <t>Requirements Management</t>
+  </si>
+  <si>
+    <t># reading user/password not implemented yet</t>
+  </si>
+  <si>
+    <t># oslc_config:mutable not available on 7.2</t>
   </si>
 </sst>
 </file>
@@ -807,7 +831,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -856,6 +880,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1173,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CC5532-4E98-4C99-BC3C-1388DFEBC8F1}">
-  <dimension ref="A1:AI111"/>
+  <dimension ref="A1:AI112"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" style="1" customWidth="1"/>
@@ -3588,6 +3615,9 @@
       </c>
     </row>
     <row r="59" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="9" t="s">
+        <v>240</v>
+      </c>
       <c r="B59" s="9" t="s">
         <v>75</v>
       </c>
@@ -4461,21 +4491,33 @@
       </c>
     </row>
     <row r="83" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C83" s="4">
+        <v>399</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>237</v>
+      </c>
       <c r="M83" s="11"/>
       <c r="Q83" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="W83" s="4" t="str">
-        <f t="shared" si="23"/>
-        <v>ibm</v>
-      </c>
-      <c r="X83" s="4" t="str">
-        <f t="shared" si="23"/>
-        <v>ibm</v>
-      </c>
-      <c r="Y83" s="4" t="str">
-        <f t="shared" si="24"/>
-        <v>https://jazz.ibm.com:9443</v>
+        <v>238</v>
+      </c>
+      <c r="W83" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y83" s="18" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="84" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -5312,11 +5354,17 @@
       <c r="P111" s="2"/>
       <c r="Y111" s="12"/>
     </row>
+    <row r="112" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A112" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="Y2" r:id="rId1" xr:uid="{2ACC8BDC-C889-4943-94E4-152B5ED32C84}"/>
+    <hyperlink ref="Y83" r:id="rId2" xr:uid="{47F31468-FF56-4E3C-A18D-949B7208F813}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>